--- a/T&Cs/test_NPD_file.xlsx
+++ b/T&Cs/test_NPD_file.xlsx
@@ -1,381 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex.miyake\coding\T&amp;Cs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7C1E6A-4009-47A7-899F-510E40CEAB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Promo &amp; GWP Status Tracker" sheetId="1" r:id="rId1"/>
-    <sheet name="T&amp;Cs 2026" sheetId="2" r:id="rId2"/>
-    <sheet name="T&amp;Cs Original" sheetId="3" r:id="rId3"/>
-    <sheet name="T&amp;Cs 2027" sheetId="4" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promo &amp; GWP Status Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T&amp;Cs 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T&amp;Cs Original" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T&amp;Cs 2027" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="65">
-  <si>
-    <t>UNIQUE ID</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>BRAND</t>
-  </si>
-  <si>
-    <t>PROMOTION TYPE</t>
-  </si>
-  <si>
-    <t>MECHANIC</t>
-  </si>
-  <si>
-    <t>DISCOUNTED/BONUS
-EAN(s) &amp; CATEGORY IDs
-(N/A If Sitewide)</t>
-  </si>
-  <si>
-    <t>COUPON CODE(S)
-(IF APPLICABLE)</t>
-  </si>
-  <si>
-    <t>MONTH</t>
-  </si>
-  <si>
-    <t>PLANNED GO LIVE DATE (00:00)</t>
-  </si>
-  <si>
-    <t>PLANNED END  DATE (00:00)</t>
-  </si>
-  <si>
-    <t>TESTING NOTES</t>
-  </si>
-  <si>
-    <t>SKINC</t>
-  </si>
-  <si>
-    <t>% OFF</t>
-  </si>
-  <si>
-    <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-BONUS:
-ultimate-anti-wrinkle-power-pair
-glass-skin-power-pair
-plumping-anti-ageing-power-pair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A </t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>has T&amp;C</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-BONUS:
-A.G.E. Defying Power Pair
-A.G.E. Reversing Face Power Pair
-A.G.E. Reversing Face &amp; Eye Power Pair</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>doesn’t have T&amp;C yet</t>
-  </si>
-  <si>
-    <t>GWP</t>
-  </si>
-  <si>
-    <t>CRM GWP VIPS 
-PTIOX 15ml
-AGE Interrupter Adv 15ml</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-BONUS:
-WYS £165
-PTIOX 15ml
-AGE Interrupter Adv 15ml</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>no T&amp;C, watch strikethrough</t>
-  </si>
-  <si>
-    <t>CRM GWP L/M Buyers
-PTIOX 4ml</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-BONUS:
-WYS £
-PTIOX 4ml - 3337875898461</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>31/04/2026</t>
-  </si>
-  <si>
-    <t>CRM GWP WYS £165 400 VIPS + MEDIUM BUYERS FREE PTIOX 15ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUALIFYING: PRICE MORE THAN 1.00
-BONUS PRODUCT: 
-WYS £165, 3337875898478
-</t>
-  </si>
-  <si>
-    <t>400 unique codes</t>
-  </si>
-  <si>
-    <t>2025 EG</t>
-  </si>
-  <si>
-    <t>VIRTUAL BUNDLES 10% OFF - POWER PAIRS</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-BONUS:
-AntiWrinkle Power Pair
-GlassSkin Power Pair
-Ultimate Anti Wrinkle Power Pair</t>
-  </si>
-  <si>
-    <t>2025 and no T&amp;C</t>
-  </si>
-  <si>
-    <t>LRP UK</t>
-  </si>
-  <si>
-    <t>Sitewide Tiered GWP</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-Tier1: WYS £40, Lipikar
-Tier2: WYS £50, Anthelios
-Tier3: WYS £60, Supramolecular
-EANs: 3337875862011 Lipikar Balm 15ml
-3337875847414 Anthelios UV Mune 15ml
-3337875950336 Supra Cleanser 15ml</t>
-  </si>
-  <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>31/09/2026</t>
-  </si>
-  <si>
-    <t>Paid Search Valentines S25% Flash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUALIFYING: PRICE MORE THAN 1.00
-</t>
-  </si>
-  <si>
-    <t>Sitewide AOX Virtual Bundles GWP</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-WYB AOX serum: 635494328202 OR 635494363210 OR 3337875746267
-BONUS:
-3337875717779 AND X 2 3337875770477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM 15% SKC X KERASTASE COLLAB </t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00</t>
-  </si>
-  <si>
-    <t>100,000 Unique Codes</t>
-  </si>
-  <si>
-    <t>GWP / % OFF</t>
-  </si>
-  <si>
-    <t>Affiliates 'Perks at Work' GWP &amp; S20% Welcome reminder Q2</t>
-  </si>
-  <si>
-    <t>QUALIFYING: PRICE MORE THAN 1.00
-WYS 40
-EAN:
-3337875824026 2x Cica Balm 3ml</t>
-  </si>
-  <si>
-    <t>mechanic edge case</t>
-  </si>
-  <si>
-    <t>UNIQUE PROMO ID</t>
-  </si>
-  <si>
-    <t>START DATE</t>
-  </si>
-  <si>
-    <t>END DATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT T&amp;Cs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG T&amp;Cs </t>
-  </si>
-  <si>
-    <t>skinc</t>
-  </si>
-  <si>
-    <t>*Receive 10% off  when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Receive 10% off when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.
-T&amp;CS
-Closing date:
-Until 2345 on 31.01.2026
-Conditions of offer:
-18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
-Online qualifications:
-Offer available at www.skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
-  </si>
-  <si>
-    <t>Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk*
-*until 2345 on 30.04.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk. Apply code at checkout.
-*until 2345 on 30.04.2026.
-T&amp;CS
-Closing date:
-*until 2345 on 30.04.2026
-Conditions of offer:
-18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
-Online qualifications:
-Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
-  </si>
-  <si>
-    <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk. Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Subject to availability, whilst stocks last.</t>
-  </si>
-  <si>
-    <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk.
-T&amp;Cs
-Closing date:
-Until 23.45 on 2026-01-31
-Conditions of offer:
-18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
-Online qualifications:
-Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Century Gothic"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,107 +200,111 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2 2 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2 2 4" xfId="1"/>
   </cellStyles>
   <dxfs count="170">
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -592,27 +314,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -623,7 +345,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -633,7 +355,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -643,7 +365,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -653,7 +375,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -663,7 +385,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -673,7 +395,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -683,7 +405,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -693,27 +415,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -723,27 +445,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -754,7 +476,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -765,7 +487,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -775,7 +497,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -785,7 +507,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -796,7 +518,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -807,7 +529,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -848,7 +570,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -858,7 +580,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -868,7 +590,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -878,7 +600,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -888,7 +610,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -898,7 +620,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -908,7 +630,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -918,27 +640,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -948,27 +670,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -979,7 +701,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -990,7 +712,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1000,7 +722,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1010,7 +732,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1021,7 +743,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1032,7 +754,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1073,7 +795,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1083,7 +805,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1093,7 +815,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1103,7 +825,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1113,7 +835,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1123,7 +845,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1133,7 +855,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1143,7 +865,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1153,7 +875,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1163,37 +885,37 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1203,7 +925,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1213,47 +935,47 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1263,27 +985,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1293,47 +1015,47 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1343,17 +1065,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1363,27 +1085,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1393,37 +1115,37 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1433,17 +1155,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1453,17 +1175,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1473,47 +1195,47 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1523,7 +1245,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1533,27 +1255,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1563,17 +1285,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1583,37 +1305,37 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1623,47 +1345,47 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1673,7 +1395,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1683,17 +1405,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1703,47 +1425,47 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1753,7 +1475,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1763,27 +1485,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1793,37 +1515,37 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1833,27 +1555,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1863,27 +1585,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1893,27 +1615,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1923,27 +1645,27 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1954,7 +1676,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1965,7 +1687,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1976,7 +1698,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1987,7 +1709,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1998,7 +1720,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2009,7 +1731,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2019,7 +1741,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2029,7 +1751,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2040,7 +1762,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2050,7 +1772,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2060,7 +1782,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2071,17 +1793,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2091,17 +1813,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -2111,17 +1833,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.5999633777886288"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2132,7 +1854,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2143,7 +1865,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2154,7 +1876,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2165,7 +1887,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2176,7 +1898,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2187,7 +1909,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2198,7 +1920,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2209,7 +1931,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -2310,14 +2032,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2637,1087 +2419,1371 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A4:L15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="65" style="10" customWidth="1"/>
-    <col min="7" max="7" width="34.6640625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="17" style="10" customWidth="1"/>
-    <col min="12" max="12" width="39.109375" bestFit="1" customWidth="1"/>
+    <col width="18.33203125" customWidth="1" style="10" min="1" max="1"/>
+    <col width="19.44140625" customWidth="1" style="10" min="2" max="2"/>
+    <col width="14.6640625" customWidth="1" style="10" min="3" max="3"/>
+    <col width="13.5546875" customWidth="1" style="10" min="4" max="4"/>
+    <col width="21.109375" customWidth="1" style="10" min="5" max="5"/>
+    <col width="65" customWidth="1" style="10" min="6" max="6"/>
+    <col width="34.6640625" customWidth="1" style="10" min="7" max="7"/>
+    <col width="18.5546875" customWidth="1" style="10" min="8" max="8"/>
+    <col width="14.109375" customWidth="1" style="10" min="9" max="9"/>
+    <col width="19.33203125" customWidth="1" style="10" min="10" max="10"/>
+    <col width="17" customWidth="1" style="10" min="11" max="11"/>
+    <col width="39.109375" bestFit="1" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>10</v>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>UNIQUE ID</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>UNIQUE ID</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>BRAND</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>PROMOTION TYPE</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>MECHANIC</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>DISCOUNTED/BONUS
+EAN(s) &amp; CATEGORY IDs
+(N/A If Sitewide)</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>COUPON CODE(S)
+(IF APPLICABLE)</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>PLANNED GO LIVE DATE (00:00)</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>PLANNED END  DATE (00:00)</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>TESTING NOTES</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" ht="129.75" customHeight="1">
+      <c r="A5" s="1" t="n">
         <v>928</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>% OFF</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+BONUS:
+ultimate-anti-wrinkle-power-pair
+glass-skin-power-pair
+plumping-anti-ageing-power-pair</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A </t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>46023</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="9" t="n">
         <v>46053</v>
       </c>
-      <c r="L5" t="s">
-        <v>17</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>has T&amp;C</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="6" ht="129.75" customHeight="1">
+      <c r="A6" s="1" t="n">
         <v>929</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="9">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>% OFF</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+BONUS:
+A.G.E. Defying Power Pair
+A.G.E. Reversing Face Power Pair
+A.G.E. Reversing Face &amp; Eye Power Pair</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A </t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
         <v>46054</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="9" t="n">
         <v>46081</v>
       </c>
-      <c r="L6" t="s">
-        <v>20</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>doesn’t have T&amp;C yet</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" ht="126" customHeight="1">
+      <c r="A7" s="1" t="n">
         <v>943</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="9">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>CRM GWP VIPS 
+PTIOX 15ml
+AGE Interrupter Adv 15ml</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+BONUS:
+WYS £165
+PTIOX 15ml
+AGE Interrupter Adv 15ml</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
         <v>46082</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="9" t="n">
         <v>46112</v>
       </c>
-      <c r="L7" t="s">
-        <v>25</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>no T&amp;C, watch strikethrough</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" ht="108" customHeight="1">
+      <c r="A8" s="1" t="n">
         <v>944</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="9">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>CRM GWP L/M Buyers
+PTIOX 4ml</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+BONUS:
+WYS £
+PTIOX 4ml - 3337875898461</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
         <v>46113</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>31/04/2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>has T&amp;C</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" ht="108" customHeight="1">
+      <c r="A9" s="1" t="n">
         <v>819</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>CRM GWP WYS £165 400 VIPS + MEDIUM BUYERS FREE PTIOX 15ml</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUALIFYING: PRICE MORE THAN 1.00
+BONUS PRODUCT: 
+WYS £165, 3337875898478
+</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>400 unique codes</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>45658</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="9" t="n">
         <v>45688</v>
       </c>
-      <c r="L9" t="s">
-        <v>33</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2025 EG</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" ht="126" customHeight="1">
+      <c r="A10" s="1" t="n">
         <v>818</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>% OFF</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>VIRTUAL BUNDLES 10% OFF - POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+BONUS:
+AntiWrinkle Power Pair
+GlassSkin Power Pair
+Ultimate Anti Wrinkle Power Pair</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A </t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>45658</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="9" t="n">
         <v>45688</v>
       </c>
-      <c r="L10" t="s">
-        <v>36</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2025 and no T&amp;C</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="234" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="11" ht="234" customHeight="1">
+      <c r="A11" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="9">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>LRP UK</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Sitewide Tiered GWP</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+Tier1: WYS £40, Lipikar
+Tier2: WYS £50, Anthelios
+Tier3: WYS £60, Supramolecular
+EANs: 3337875862011 Lipikar Balm 15ml
+3337875847414 Anthelios UV Mune 15ml
+3337875950336 Supra Cleanser 15ml</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
         <v>46266</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>41</v>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>31/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="1" t="n">
         <v>1031</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="9">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>LRP UK</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>% OFF</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Paid Search Valentines S25% Flash</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUALIFYING: PRICE MORE THAN 1.00
+</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
         <v>46066</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="9" t="n">
         <v>46067</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="198" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+    <row r="13" ht="198" customHeight="1">
+      <c r="A13" s="1" t="n">
         <v>1032</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>GWP</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Sitewide AOX Virtual Bundles GWP</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+WYB AOX serum: 635494328202 OR 635494363210 OR 3337875746267
+BONUS:
+3337875717779 AND X 2 3337875770477</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
         <v>46082</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="9" t="n">
         <v>46112</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="1" t="n">
         <v>1014</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="9">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>% OFF</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRM 15% SKC X KERASTASE COLLAB </t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>100,000 Unique Codes</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
         <v>46078</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="9" t="n">
         <v>46120</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+    <row r="15" ht="126" customHeight="1">
+      <c r="A15" s="1" t="n">
         <v>1042</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="9">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>LRP UK</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>GWP / % OFF</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Affiliates 'Perks at Work' GWP &amp; S20% Welcome reminder Q2</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>QUALIFYING: PRICE MORE THAN 1.00
+WYS 40
+EAN:
+3337875824026 2x Cica Balm 3ml</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
         <v>46113</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="9" t="n">
         <v>46203</v>
       </c>
-      <c r="L15" t="s">
-        <v>52</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>mechanic edge case</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="169" priority="203"/>
+    <cfRule type="duplicateValues" priority="203" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A8">
-    <cfRule type="duplicateValues" dxfId="168" priority="180"/>
+    <cfRule type="duplicateValues" priority="180" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="167" priority="160"/>
+    <cfRule type="duplicateValues" priority="160" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="166" priority="146"/>
+    <cfRule type="duplicateValues" priority="146" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="165" priority="126"/>
+    <cfRule type="duplicateValues" priority="126" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="164" priority="93"/>
+    <cfRule type="duplicateValues" priority="93" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="163" priority="74"/>
+    <cfRule type="duplicateValues" priority="74" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="162" priority="47"/>
+    <cfRule type="duplicateValues" priority="47" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="161" priority="26"/>
+    <cfRule type="duplicateValues" priority="26" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:E8">
-    <cfRule type="cellIs" dxfId="160" priority="187" operator="equal">
+    <cfRule type="cellIs" priority="187" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:E9">
-    <cfRule type="cellIs" dxfId="159" priority="167" operator="equal">
+    <cfRule type="cellIs" priority="167" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:E10">
-    <cfRule type="cellIs" dxfId="158" priority="153" operator="equal">
+    <cfRule type="cellIs" priority="153" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11:E11">
-    <cfRule type="cellIs" dxfId="157" priority="133" operator="equal">
+    <cfRule type="cellIs" priority="133" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13:E13">
-    <cfRule type="cellIs" dxfId="156" priority="81" operator="equal">
+    <cfRule type="cellIs" priority="81" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:E14">
-    <cfRule type="cellIs" dxfId="155" priority="48" operator="equal">
+    <cfRule type="cellIs" priority="48" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:E15">
-    <cfRule type="cellIs" dxfId="154" priority="33" operator="equal">
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:K6">
-    <cfRule type="cellIs" dxfId="153" priority="171" operator="equal">
+    <cfRule type="cellIs" priority="171" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:K12">
-    <cfRule type="cellIs" dxfId="152" priority="90" operator="equal">
+    <cfRule type="cellIs" priority="90" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C8 J5:J8">
-    <cfRule type="containsText" dxfId="151" priority="185" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="185" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",C5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="150" priority="186" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="186" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",C5)))</formula>
     </cfRule>
+    <cfRule type="containsText" priority="184" operator="containsText" dxfId="2" text="BACK POCKET">
+      <formula>NOT(ISERROR(SEARCH("BACK POCKET",C5)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C15">
-    <cfRule type="containsText" dxfId="149" priority="30" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="30" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="32" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="32" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",C9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="147" priority="31" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="31" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",C9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D8">
-    <cfRule type="containsText" dxfId="146" priority="181" operator="containsText" text="SKINC">
+    <cfRule type="containsText" priority="181" operator="containsText" dxfId="20" text="SKINC">
       <formula>NOT(ISERROR(SEARCH("SKINC",D5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="145" priority="182" operator="containsText" text="DECLEOR">
+    <cfRule type="containsText" priority="182" operator="containsText" dxfId="19" text="DECLEOR">
       <formula>NOT(ISERROR(SEARCH("DECLEOR",D5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="183" operator="containsText" text="LRP UK">
+    <cfRule type="containsText" priority="183" operator="containsText" dxfId="18" text="LRP UK">
       <formula>NOT(ISERROR(SEARCH("LRP UK",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="containsText" dxfId="143" priority="27" operator="containsText" text="SKINC">
+    <cfRule type="containsText" priority="27" operator="containsText" dxfId="20" text="SKINC">
       <formula>NOT(ISERROR(SEARCH("SKINC",D9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="28" operator="containsText" text="DECLEOR">
+    <cfRule type="containsText" priority="28" operator="containsText" dxfId="19" text="DECLEOR">
       <formula>NOT(ISERROR(SEARCH("DECLEOR",D9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="141" priority="29" operator="containsText" text="LRP UK">
+    <cfRule type="containsText" priority="29" operator="containsText" dxfId="18" text="LRP UK">
       <formula>NOT(ISERROR(SEARCH("LRP UK",D9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:K8">
-    <cfRule type="cellIs" dxfId="140" priority="179" operator="equal">
+    <cfRule type="cellIs" priority="179" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:K10">
-    <cfRule type="cellIs" dxfId="139" priority="145" operator="equal">
+    <cfRule type="cellIs" priority="145" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:K11">
-    <cfRule type="cellIs" dxfId="138" priority="125" operator="equal">
+    <cfRule type="cellIs" priority="125" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:K13">
-    <cfRule type="cellIs" dxfId="137" priority="73" operator="equal">
+    <cfRule type="cellIs" priority="73" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:K14">
-    <cfRule type="cellIs" dxfId="136" priority="46" operator="equal">
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:K15">
-    <cfRule type="cellIs" dxfId="135" priority="25" operator="equal">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10">
-    <cfRule type="containsText" dxfId="134" priority="140" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="140" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="133" priority="141" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="141" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="142" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="142" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:G11">
-    <cfRule type="containsText" dxfId="131" priority="120" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="120" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="119" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="119" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="121" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="121" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="128" priority="110" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="110" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="127" priority="111" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="111" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="112" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="112" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="125" priority="107" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="107" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="124" priority="113" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="113" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="123" priority="106" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="106" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="122" priority="105" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="105" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="121" priority="104" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="104" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="120" priority="114" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="114" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="119" priority="115" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="115" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="118" priority="116" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="116" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="117" priority="117" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="117" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="116" priority="118" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="118" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="115" priority="109" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="109" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="114" priority="108" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="108" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="113" priority="71" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="71" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="64" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="64" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="111" priority="65" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="65" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="66" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="66" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="109" priority="70" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="70" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="72" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="72" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13:G14">
-    <cfRule type="containsText" dxfId="107" priority="45" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="45" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="43" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="43" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="44" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="44" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="104" priority="17" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="17" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="16" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="16" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="15" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="15" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="14" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="14" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="13" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="13" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="23" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="23" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="18" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="18" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="22" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="22" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="24" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="24" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H8">
-    <cfRule type="containsText" dxfId="95" priority="169" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="169" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="168" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="168" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="170" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="170" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H11">
-    <cfRule type="containsText" dxfId="92" priority="124" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="124" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="122" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="122" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="123" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="123" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13:H13">
-    <cfRule type="containsText" dxfId="89" priority="67" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="67" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="68" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="68" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="69" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="69" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14:H14">
-    <cfRule type="containsText" dxfId="86" priority="41" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="41" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="42" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="42" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="40" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="40" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15:H15">
-    <cfRule type="containsText" dxfId="83" priority="21" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="21" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="20" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="20" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",G15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="19" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="19" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",G15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H10 J9:J10">
-    <cfRule type="containsText" dxfId="80" priority="150" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="150" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",H9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H10">
-    <cfRule type="containsText" dxfId="79" priority="144" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="144" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",H9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="143" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="143" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",H9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="77" priority="87" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="87" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",H12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="89" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="89" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",H12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="88" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="88" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",H12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="containsText" dxfId="74" priority="39" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="39" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",H14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="37" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="37" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",H14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="38" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="38" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",H14)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J8 C5:C8">
-    <cfRule type="containsText" dxfId="71" priority="184" operator="containsText" text="BACK POCKET">
-      <formula>NOT(ISERROR(SEARCH("BACK POCKET",C5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J9:J11">
-    <cfRule type="containsText" dxfId="70" priority="131" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="131" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",J9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="132" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="132" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",J9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="68" priority="130" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="130" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12">
-    <cfRule type="containsText" dxfId="67" priority="97" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="97" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12:J14">
-    <cfRule type="containsText" dxfId="66" priority="54" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="54" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",J12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="53" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="53" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",J12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="64" priority="78" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="78" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14">
-    <cfRule type="containsText" dxfId="63" priority="52" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="52" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="62" priority="4" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="6" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="6" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",J15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="12" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="12" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",J15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="10" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="10" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",J15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",J15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="11" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="11" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",J15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K8">
-    <cfRule type="containsText" dxfId="56" priority="173" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="173" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",K5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="174" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="174" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",K5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="175" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="175" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",K5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K15">
-    <cfRule type="containsText" dxfId="53" priority="7" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="7" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",K9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="8" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="8" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",K9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="9" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="9" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",K9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="50" priority="2" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",K15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="1" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",K15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",K15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"arial"&amp;9 &amp;K008000_x000D_# C1 - Internal use</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"arial"&amp;9 &amp;K008000_x000d_# C1 - Internal use</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="40.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="87" customWidth="1"/>
-    <col min="8" max="8" width="50" bestFit="1" customWidth="1"/>
+    <col width="13.5546875" customWidth="1" min="1" max="1"/>
+    <col width="40.6640625" customWidth="1" min="4" max="4"/>
+    <col width="15.6640625" customWidth="1" min="5" max="5"/>
+    <col width="13.44140625" customWidth="1" min="6" max="6"/>
+    <col width="87" customWidth="1" min="7" max="7"/>
+    <col width="50" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>57</v>
+    <row r="1" ht="38.25" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>UNIQUE PROMO ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>BRAND</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>MECHANIC</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>START DATE</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>END DATE</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHORT T&amp;Cs </t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LONG T&amp;Cs </t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="263.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" ht="263.25" customHeight="1">
+      <c r="A2" s="1" t="n">
         <v>928</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>skinc</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>46023</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="9" t="n">
         <v>46053</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>60</v>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>*Receive 10% off  when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*Receive 10% off when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.
+T&amp;CS
+Closing date:
+Until 2345 on 31.01.2026
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at www.skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="351" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
+    <row r="3" ht="351" customHeight="1">
+      <c r="A3" s="22" t="n">
         <v>944</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>skinc</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CRM GWP L/M Buyers
+PTIOX 4ml</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="n">
         <v>46113</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="24" t="n">
         <v>46142</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>62</v>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk*
+*until 2345 on 30.04.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk. Apply code at checkout.
+*until 2345 on 30.04.2026.
+T&amp;CS
+Closing date:
+*until 2345 on 30.04.2026
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="330" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
+    <row r="4" ht="330" customHeight="1">
+      <c r="A4" s="22" t="n">
         <v>928</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="24">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="n">
         <v>46023</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="29" t="n">
         <v>46053</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>64</v>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk. Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Subject to availability, whilst stocks last.</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk.
+T&amp;Cs
+Closing date:
+Until 23.45 on 2026-01-31
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="47" priority="31"/>
+    <cfRule type="duplicateValues" priority="31" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="46" priority="5"/>
+    <cfRule type="duplicateValues" priority="5" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="duplicateValues" dxfId="45" priority="22"/>
-    <cfRule type="cellIs" dxfId="44" priority="23" operator="equal">
+    <cfRule type="duplicateValues" priority="22" dxfId="23"/>
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B2">
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="equal">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C4">
-    <cfRule type="containsText" dxfId="42" priority="14" operator="containsText" text="SKINC">
+    <cfRule type="containsText" priority="14" operator="containsText" dxfId="20" text="SKINC">
       <formula>NOT(ISERROR(SEARCH("SKINC",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="15" operator="containsText" text="DECLEOR">
+    <cfRule type="containsText" priority="15" operator="containsText" dxfId="19" text="DECLEOR">
       <formula>NOT(ISERROR(SEARCH("DECLEOR",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="16" operator="containsText" text="LRP UK">
+    <cfRule type="containsText" priority="16" operator="containsText" dxfId="18" text="LRP UK">
       <formula>NOT(ISERROR(SEARCH("LRP UK",C2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="17" operator="equal">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F3">
-    <cfRule type="cellIs" dxfId="38" priority="13" operator="equal">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="containsText" dxfId="37" priority="10" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="10" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="11" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="11" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="12" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="12" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
-    <cfRule type="containsText" dxfId="34" priority="28" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="28" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="29" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="29" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="30" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="30" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="containsText" dxfId="31" priority="7" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="7" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",F2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="8" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="8" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",F2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="9" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F4">
-    <cfRule type="containsText" dxfId="28" priority="19" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="19" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="20" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="20" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="21" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:F4">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F4">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",E4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3726,176 +3792,233 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="45.5546875" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="7" width="74.21875" customWidth="1"/>
-    <col min="8" max="8" width="61.6640625" customWidth="1"/>
+    <col width="20.44140625" customWidth="1" min="1" max="1"/>
+    <col width="14.21875" customWidth="1" min="2" max="2"/>
+    <col width="15.44140625" customWidth="1" min="3" max="3"/>
+    <col width="45.5546875" customWidth="1" min="4" max="4"/>
+    <col width="16.109375" customWidth="1" min="5" max="5"/>
+    <col width="14.77734375" customWidth="1" min="6" max="6"/>
+    <col width="74.21875" customWidth="1" min="7" max="7"/>
+    <col width="61.6640625" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>57</v>
+    <row r="1" ht="63" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>UNIQUE PROMO ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>MONTH</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>BRAND</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>MECHANIC</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>START DATE</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>END DATE</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHORT T&amp;Cs </t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LONG T&amp;Cs </t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" ht="303.6" customHeight="1">
+      <c r="A2" s="1" t="n">
         <v>928</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>skinc</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>46023</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="9" t="n">
         <v>46053</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>60</v>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>*Receive 10% off  when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*Receive 10% off when you buy selected products online at www.skinceuticals.co.uk. Until 2345 on 31.01.2026. Valid online at www.skinceuticals.co.uk.
+T&amp;CS
+Closing date:
+Until 2345 on 31.01.2026
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at www.skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="303.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
+    <row r="3" ht="303.6" customHeight="1">
+      <c r="A3" s="22" t="n">
         <v>944</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>skinc</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CRM GWP L/M Buyers
+PTIOX 4ml</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="n">
         <v>46113</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="24" t="n">
         <v>46142</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>62</v>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk*
+*until 2345 on 30.04.2026. Valid online at www.skinceuticals.co.uk.  Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Subject to availability, whilst stocks last.</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Receive a complimentary PTIOX sample when you shop online at www.skinceuticals.co.uk. Apply code at checkout.
+*until 2345 on 30.04.2026.
+T&amp;CS
+Closing date:
+*until 2345 on 30.04.2026
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid.  Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems.  Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA. </t>
+        </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
+    <cfRule type="duplicateValues" priority="14" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" priority="1" dxfId="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="duplicateValues" priority="19" dxfId="23"/>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B2">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C3">
-    <cfRule type="containsText" dxfId="20" priority="10" operator="containsText" text="SKINC">
+    <cfRule type="containsText" priority="10" operator="containsText" dxfId="20" text="SKINC">
       <formula>NOT(ISERROR(SEARCH("SKINC",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="DECLEOR">
+    <cfRule type="containsText" priority="11" operator="containsText" dxfId="19" text="DECLEOR">
       <formula>NOT(ISERROR(SEARCH("DECLEOR",C2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="12" operator="containsText" text="LRP UK">
+    <cfRule type="containsText" priority="12" operator="containsText" dxfId="18" text="LRP UK">
       <formula>NOT(ISERROR(SEARCH("LRP UK",C2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:F3">
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="3">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="6" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="7" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="7" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="8" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
-    <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="BACK POCKET">
+    <cfRule type="containsText" priority="25" operator="containsText" dxfId="2" text="BACK POCKET">
       <formula>NOT(ISERROR(SEARCH("BACK POCKET",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="26" operator="containsText" text="TBC">
+    <cfRule type="containsText" priority="26" operator="containsText" dxfId="1" text="TBC">
       <formula>NOT(ISERROR(SEARCH("TBC",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="27" operator="containsText" text="CONFIRMED">
+    <cfRule type="containsText" priority="27" operator="containsText" dxfId="0" text="CONFIRMED">
       <formula>NOT(ISERROR(SEARCH("CONFIRMED",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",F2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",F2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",F2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="LOW">
+    <cfRule type="containsText" priority="16" operator="containsText" dxfId="6" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="MEDIUM">
+    <cfRule type="containsText" priority="17" operator="containsText" dxfId="5" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="HIGH">
+    <cfRule type="containsText" priority="18" operator="containsText" dxfId="4" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3904,62 +4027,98 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A4:H5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.21875" customWidth="1"/>
+    <col width="19" bestFit="1" customWidth="1" min="4" max="5"/>
+    <col width="255.77734375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="36.21875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>928</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="28">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SAVE 10% - VIRTUAL BUNDLES POWER PAIRS</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="n">
         <v>46023</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="28" t="n">
         <v>46053</v>
       </c>
-      <c r="G4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" t="s">
-        <v>63</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk.
+T&amp;Cs
+Closing date:
+Until 23.45 on 2026-01-31
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk. Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Subject to availability, whilst stocks last.</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" ht="409.6" customHeight="1">
+      <c r="A5" t="n">
         <v>928</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="25">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SKINC</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="n">
         <v>46023</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="28" t="n">
         <v>46053</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>63</v>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk.
+T&amp;Cs
+Closing date:
+Until 23.45 on 2026-01-31
+Conditions of offer:
+18+ only, one transaction per customer, UK only. This promotion is not available in conjunction with any other offers. Subject to availability, whilst stocks last.
+Online qualifications:
+Offer available at skinceuticals.co.uk Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Promoter: SkinCeuticals, a trading division of L’Oréal (U.K.) Limited, Gateway Central White City Place 187 Wood Lane, London W12 7SA.</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>*Receive a complimentary gift when you spend £65 online at www.skinceuticals.co.uk. Until 23.45 on 2026-01-31 Valid online at www.skinceuticals.co.uk. Incomplete, illegal, misdirected or late redemptions will not be valid. Promoter is not responsible for redemptions lost, damaged or delayed due to technical or connectivity or other problems. Subject to availability, whilst stocks last.</t>
+        </is>
       </c>
     </row>
   </sheetData>
